--- a/backend/MEMORIA TECNICA PRUEBAS - CTC.xlsx
+++ b/backend/MEMORIA TECNICA PRUEBAS - CTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\memoria-tecnica-app\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4C2BC8-0484-4502-AAE0-D8A28E9A6636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498C504F-A6B8-42FD-A366-AD9AA91258D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="377" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="377" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CTC" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="526">
   <si>
     <t>HUB1</t>
   </si>
@@ -1572,6 +1572,45 @@
   </si>
   <si>
     <t>DISPONIBLE 25</t>
+  </si>
+  <si>
+    <t>CONTACTO NOMBRE</t>
+  </si>
+  <si>
+    <t>CONTACTO TELEFONO</t>
+  </si>
+  <si>
+    <t>EDGAR PESCADOR</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>TOñO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>JULIAN</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
   </si>
 </sst>
 </file>
@@ -2645,7 +2684,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:XFC139"/>
+  <dimension ref="A1:XFD139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.375" style="1" customWidth="1"/>
@@ -2676,12 +2715,11 @@
     <col min="29" max="29" width="16.25" style="1" customWidth="1"/>
     <col min="30" max="30" width="10.25" style="1" customWidth="1"/>
     <col min="31" max="37" width="11.25" style="1" hidden="1" customWidth="1"/>
-    <col min="38" max="39" width="11" style="1" customWidth="1"/>
-    <col min="40" max="16383" width="11" style="1" hidden="1"/>
-    <col min="16384" max="16384" width="7" style="1" hidden="1"/>
+    <col min="38" max="41" width="11" style="1" customWidth="1"/>
+    <col min="42" max="16384" width="11" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>55</v>
       </c>
@@ -2782,8 +2820,14 @@
       <c r="AM1" s="22" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="2" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN1" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="AO1" s="22" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
         <v>74</v>
       </c>
@@ -2865,8 +2909,10 @@
       <c r="AE2" s="7"/>
       <c r="AL2" s="74"/>
       <c r="AM2" s="74"/>
-    </row>
-    <row r="3" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN2" s="74"/>
+      <c r="AO2" s="74"/>
+    </row>
+    <row r="3" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
         <v>74</v>
       </c>
@@ -2948,8 +2994,10 @@
       <c r="AE3" s="8"/>
       <c r="AL3" s="74"/>
       <c r="AM3" s="74"/>
-    </row>
-    <row r="4" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN3" s="74"/>
+      <c r="AO3" s="74"/>
+    </row>
+    <row r="4" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
         <v>74</v>
       </c>
@@ -3031,8 +3079,10 @@
       <c r="AE4" s="8"/>
       <c r="AL4" s="74"/>
       <c r="AM4" s="74"/>
-    </row>
-    <row r="5" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN4" s="74"/>
+      <c r="AO4" s="74"/>
+    </row>
+    <row r="5" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>74</v>
       </c>
@@ -3114,8 +3164,10 @@
       <c r="AE5" s="8"/>
       <c r="AL5" s="74"/>
       <c r="AM5" s="74"/>
-    </row>
-    <row r="6" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN5" s="74"/>
+      <c r="AO5" s="74"/>
+    </row>
+    <row r="6" spans="1:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
         <v>74</v>
       </c>
@@ -3167,8 +3219,10 @@
       <c r="AE6" s="8"/>
       <c r="AL6" s="74"/>
       <c r="AM6" s="74"/>
-    </row>
-    <row r="7" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN6" s="74"/>
+      <c r="AO6" s="74"/>
+    </row>
+    <row r="7" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
         <v>74</v>
       </c>
@@ -3250,8 +3304,10 @@
       <c r="AE7" s="8"/>
       <c r="AL7" s="74"/>
       <c r="AM7" s="74"/>
-    </row>
-    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN7" s="74"/>
+      <c r="AO7" s="74"/>
+    </row>
+    <row r="8" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
         <v>74</v>
       </c>
@@ -3303,8 +3359,10 @@
       <c r="AE8" s="8"/>
       <c r="AL8" s="74"/>
       <c r="AM8" s="74"/>
-    </row>
-    <row r="9" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN8" s="74"/>
+      <c r="AO8" s="74"/>
+    </row>
+    <row r="9" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
         <v>74</v>
       </c>
@@ -3386,8 +3444,10 @@
       <c r="AE9" s="8"/>
       <c r="AL9" s="74"/>
       <c r="AM9" s="74"/>
-    </row>
-    <row r="10" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN9" s="74"/>
+      <c r="AO9" s="74"/>
+    </row>
+    <row r="10" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
         <v>74</v>
       </c>
@@ -3441,8 +3501,10 @@
       <c r="AE10" s="8"/>
       <c r="AL10" s="74"/>
       <c r="AM10" s="74"/>
-    </row>
-    <row r="11" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN10" s="74"/>
+      <c r="AO10" s="74"/>
+    </row>
+    <row r="11" spans="1:41" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
         <v>74</v>
       </c>
@@ -3496,8 +3558,10 @@
       <c r="AE11" s="8"/>
       <c r="AL11" s="74"/>
       <c r="AM11" s="74"/>
-    </row>
-    <row r="12" spans="1:39" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN11" s="74"/>
+      <c r="AO11" s="74"/>
+    </row>
+    <row r="12" spans="1:41" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3615,10 @@
       <c r="AE12" s="8"/>
       <c r="AL12" s="74"/>
       <c r="AM12" s="74"/>
-    </row>
-    <row r="13" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN12" s="74"/>
+      <c r="AO12" s="74"/>
+    </row>
+    <row r="13" spans="1:41" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="128" t="s">
         <v>104</v>
       </c>
@@ -3596,8 +3662,10 @@
       <c r="AE13" s="8"/>
       <c r="AL13" s="74"/>
       <c r="AM13" s="74"/>
-    </row>
-    <row r="14" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN13" s="74"/>
+      <c r="AO13" s="74"/>
+    </row>
+    <row r="14" spans="1:41" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="128" t="s">
         <v>104</v>
       </c>
@@ -3641,8 +3709,10 @@
       <c r="AE14" s="8"/>
       <c r="AL14" s="74"/>
       <c r="AM14" s="74"/>
-    </row>
-    <row r="15" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN14" s="74"/>
+      <c r="AO14" s="74"/>
+    </row>
+    <row r="15" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="128" t="s">
         <v>104</v>
       </c>
@@ -3686,8 +3756,10 @@
       <c r="AE15" s="8"/>
       <c r="AL15" s="74"/>
       <c r="AM15" s="74"/>
-    </row>
-    <row r="16" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN15" s="74"/>
+      <c r="AO15" s="74"/>
+    </row>
+    <row r="16" spans="1:41" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="31" t="s">
         <v>512</v>
       </c>
@@ -3731,8 +3803,10 @@
       <c r="AE16" s="8"/>
       <c r="AL16" s="74"/>
       <c r="AM16" s="74"/>
-    </row>
-    <row r="17" spans="1:39" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN16" s="74"/>
+      <c r="AO16" s="74"/>
+    </row>
+    <row r="17" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="31" t="s">
         <v>512</v>
       </c>
@@ -3776,8 +3850,10 @@
       <c r="AE17" s="8"/>
       <c r="AL17" s="74"/>
       <c r="AM17" s="74"/>
-    </row>
-    <row r="18" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN17" s="74"/>
+      <c r="AO17" s="74"/>
+    </row>
+    <row r="18" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="31" t="s">
         <v>512</v>
       </c>
@@ -3821,8 +3897,10 @@
       <c r="AE18" s="8"/>
       <c r="AL18" s="74"/>
       <c r="AM18" s="74"/>
-    </row>
-    <row r="19" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN18" s="74"/>
+      <c r="AO18" s="74"/>
+    </row>
+    <row r="19" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="31" t="s">
         <v>511</v>
       </c>
@@ -3866,8 +3944,10 @@
       <c r="AE19" s="8"/>
       <c r="AL19" s="74"/>
       <c r="AM19" s="74"/>
-    </row>
-    <row r="20" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN19" s="74"/>
+      <c r="AO19" s="74"/>
+    </row>
+    <row r="20" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="31" t="s">
         <v>511</v>
       </c>
@@ -3911,8 +3991,10 @@
       <c r="AE20" s="8"/>
       <c r="AL20" s="74"/>
       <c r="AM20" s="74"/>
-    </row>
-    <row r="21" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN20" s="74"/>
+      <c r="AO20" s="74"/>
+    </row>
+    <row r="21" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="31" t="s">
         <v>511</v>
       </c>
@@ -3956,8 +4038,10 @@
       <c r="AE21" s="8"/>
       <c r="AL21" s="74"/>
       <c r="AM21" s="74"/>
-    </row>
-    <row r="22" spans="1:39" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN21" s="74"/>
+      <c r="AO21" s="74"/>
+    </row>
+    <row r="22" spans="1:41" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="31" t="s">
         <v>511</v>
       </c>
@@ -4001,8 +4085,10 @@
       <c r="AE22" s="8"/>
       <c r="AL22" s="74"/>
       <c r="AM22" s="74"/>
-    </row>
-    <row r="23" spans="1:39" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN22" s="74"/>
+      <c r="AO22" s="74"/>
+    </row>
+    <row r="23" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="31" t="s">
         <v>511</v>
       </c>
@@ -4046,8 +4132,10 @@
       <c r="AE23" s="8"/>
       <c r="AL23" s="74"/>
       <c r="AM23" s="74"/>
-    </row>
-    <row r="24" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN23" s="74"/>
+      <c r="AO23" s="74"/>
+    </row>
+    <row r="24" spans="1:41" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="31" t="s">
         <v>511</v>
       </c>
@@ -4091,8 +4179,10 @@
       <c r="AE24" s="8"/>
       <c r="AL24" s="74"/>
       <c r="AM24" s="74"/>
-    </row>
-    <row r="25" spans="1:39" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN24" s="74"/>
+      <c r="AO24" s="74"/>
+    </row>
+    <row r="25" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="31" t="s">
         <v>511</v>
       </c>
@@ -4136,8 +4226,10 @@
       <c r="AE25" s="8"/>
       <c r="AL25" s="74"/>
       <c r="AM25" s="74"/>
-    </row>
-    <row r="26" spans="1:39" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN25" s="74"/>
+      <c r="AO25" s="74"/>
+    </row>
+    <row r="26" spans="1:41" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="29" t="s">
         <v>74</v>
       </c>
@@ -4219,8 +4311,10 @@
       <c r="AE26" s="8"/>
       <c r="AL26" s="74"/>
       <c r="AM26" s="74"/>
-    </row>
-    <row r="27" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN26" s="74"/>
+      <c r="AO26" s="74"/>
+    </row>
+    <row r="27" spans="1:41" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="31" t="s">
         <v>511</v>
       </c>
@@ -4264,8 +4358,10 @@
       <c r="AE27" s="8"/>
       <c r="AL27" s="74"/>
       <c r="AM27" s="74"/>
-    </row>
-    <row r="28" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN27" s="74"/>
+      <c r="AO27" s="74"/>
+    </row>
+    <row r="28" spans="1:41" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="31" t="s">
         <v>511</v>
       </c>
@@ -4309,8 +4405,10 @@
       <c r="AE28" s="8"/>
       <c r="AL28" s="74"/>
       <c r="AM28" s="74"/>
-    </row>
-    <row r="29" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN28" s="74"/>
+      <c r="AO28" s="74"/>
+    </row>
+    <row r="29" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="31" t="s">
         <v>511</v>
       </c>
@@ -4354,8 +4452,10 @@
       <c r="AE29" s="8"/>
       <c r="AL29" s="74"/>
       <c r="AM29" s="74"/>
-    </row>
-    <row r="30" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN29" s="74"/>
+      <c r="AO29" s="74"/>
+    </row>
+    <row r="30" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29" t="s">
         <v>127</v>
       </c>
@@ -4405,8 +4505,10 @@
       <c r="AE30" s="8"/>
       <c r="AL30" s="74"/>
       <c r="AM30" s="74"/>
-    </row>
-    <row r="31" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN30" s="74"/>
+      <c r="AO30" s="74"/>
+    </row>
+    <row r="31" spans="1:41" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="31" t="s">
         <v>104</v>
       </c>
@@ -4450,8 +4552,10 @@
       <c r="AE31" s="8"/>
       <c r="AL31" s="74"/>
       <c r="AM31" s="74"/>
-    </row>
-    <row r="32" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN31" s="74"/>
+      <c r="AO31" s="74"/>
+    </row>
+    <row r="32" spans="1:41" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="31" t="s">
         <v>104</v>
       </c>
@@ -4495,8 +4599,10 @@
       <c r="AE32" s="8"/>
       <c r="AL32" s="74"/>
       <c r="AM32" s="74"/>
-    </row>
-    <row r="33" spans="1:39" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN32" s="74"/>
+      <c r="AO32" s="74"/>
+    </row>
+    <row r="33" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="57" t="s">
         <v>104</v>
       </c>
@@ -4542,8 +4648,10 @@
       <c r="AE33" s="8"/>
       <c r="AL33" s="74"/>
       <c r="AM33" s="74"/>
-    </row>
-    <row r="34" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN33" s="74"/>
+      <c r="AO33" s="74"/>
+    </row>
+    <row r="34" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="31" t="s">
         <v>104</v>
       </c>
@@ -4587,8 +4695,10 @@
       <c r="AE34" s="8"/>
       <c r="AL34" s="74"/>
       <c r="AM34" s="74"/>
-    </row>
-    <row r="35" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN34" s="74"/>
+      <c r="AO34" s="74"/>
+    </row>
+    <row r="35" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="31" t="s">
         <v>104</v>
       </c>
@@ -4632,8 +4742,10 @@
       <c r="AE35" s="8"/>
       <c r="AL35" s="74"/>
       <c r="AM35" s="74"/>
-    </row>
-    <row r="36" spans="1:39" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN35" s="74"/>
+      <c r="AO35" s="74"/>
+    </row>
+    <row r="36" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="31" t="s">
         <v>104</v>
       </c>
@@ -4677,8 +4789,10 @@
       <c r="AE36" s="8"/>
       <c r="AL36" s="74"/>
       <c r="AM36" s="74"/>
-    </row>
-    <row r="37" spans="1:39" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN36" s="74"/>
+      <c r="AO36" s="74"/>
+    </row>
+    <row r="37" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="31" t="s">
         <v>104</v>
       </c>
@@ -4722,8 +4836,10 @@
       <c r="AE37" s="8"/>
       <c r="AL37" s="74"/>
       <c r="AM37" s="74"/>
-    </row>
-    <row r="38" spans="1:39" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN37" s="74"/>
+      <c r="AO37" s="74"/>
+    </row>
+    <row r="38" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="31" t="s">
         <v>104</v>
       </c>
@@ -4767,8 +4883,10 @@
       <c r="AE38" s="8"/>
       <c r="AL38" s="74"/>
       <c r="AM38" s="74"/>
-    </row>
-    <row r="39" spans="1:39" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN38" s="74"/>
+      <c r="AO38" s="74"/>
+    </row>
+    <row r="39" spans="1:41" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="31" t="s">
         <v>104</v>
       </c>
@@ -4812,8 +4930,10 @@
       <c r="AE39" s="8"/>
       <c r="AL39" s="74"/>
       <c r="AM39" s="74"/>
-    </row>
-    <row r="40" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN39" s="74"/>
+      <c r="AO39" s="74"/>
+    </row>
+    <row r="40" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="29" t="s">
         <v>127</v>
       </c>
@@ -4897,8 +5017,10 @@
       <c r="AE40" s="8"/>
       <c r="AL40" s="74"/>
       <c r="AM40" s="74"/>
-    </row>
-    <row r="41" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN40" s="74"/>
+      <c r="AO40" s="74"/>
+    </row>
+    <row r="41" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="29" t="s">
         <v>127</v>
       </c>
@@ -4982,8 +5104,10 @@
       <c r="AE41" s="8"/>
       <c r="AL41" s="74"/>
       <c r="AM41" s="74"/>
-    </row>
-    <row r="42" spans="1:39" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN41" s="74"/>
+      <c r="AO41" s="74"/>
+    </row>
+    <row r="42" spans="1:41" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="69" t="s">
         <v>54</v>
       </c>
@@ -5073,8 +5197,10 @@
       <c r="AE42" s="8"/>
       <c r="AL42" s="74"/>
       <c r="AM42" s="74"/>
-    </row>
-    <row r="43" spans="1:39" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN42" s="74"/>
+      <c r="AO42" s="74"/>
+    </row>
+    <row r="43" spans="1:41" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="31" t="s">
         <v>104</v>
       </c>
@@ -5118,8 +5244,10 @@
       <c r="AE43" s="8"/>
       <c r="AL43" s="74"/>
       <c r="AM43" s="74"/>
-    </row>
-    <row r="44" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN43" s="74"/>
+      <c r="AO43" s="74"/>
+    </row>
+    <row r="44" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="31" t="s">
         <v>104</v>
       </c>
@@ -5163,8 +5291,10 @@
       <c r="AE44" s="8"/>
       <c r="AL44" s="74"/>
       <c r="AM44" s="74"/>
-    </row>
-    <row r="45" spans="1:39" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN44" s="74"/>
+      <c r="AO44" s="74"/>
+    </row>
+    <row r="45" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="31" t="s">
         <v>104</v>
       </c>
@@ -5208,8 +5338,10 @@
       <c r="AE45" s="8"/>
       <c r="AL45" s="74"/>
       <c r="AM45" s="74"/>
-    </row>
-    <row r="46" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN45" s="74"/>
+      <c r="AO45" s="74"/>
+    </row>
+    <row r="46" spans="1:41" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="31" t="s">
         <v>104</v>
       </c>
@@ -5253,8 +5385,10 @@
       <c r="AE46" s="8"/>
       <c r="AL46" s="74"/>
       <c r="AM46" s="74"/>
-    </row>
-    <row r="47" spans="1:39" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN46" s="74"/>
+      <c r="AO46" s="74"/>
+    </row>
+    <row r="47" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="29" t="s">
         <v>74</v>
       </c>
@@ -5340,8 +5474,10 @@
       <c r="AE47" s="8"/>
       <c r="AL47" s="74"/>
       <c r="AM47" s="74"/>
-    </row>
-    <row r="48" spans="1:39" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN47" s="74"/>
+      <c r="AO47" s="74"/>
+    </row>
+    <row r="48" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="31" t="s">
         <v>104</v>
       </c>
@@ -5385,8 +5521,10 @@
       <c r="AE48" s="8"/>
       <c r="AL48" s="74"/>
       <c r="AM48" s="74"/>
-    </row>
-    <row r="49" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN48" s="74"/>
+      <c r="AO48" s="74"/>
+    </row>
+    <row r="49" spans="1:41" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="29" t="s">
         <v>74</v>
       </c>
@@ -5440,8 +5578,10 @@
       <c r="AE49" s="8"/>
       <c r="AL49" s="74"/>
       <c r="AM49" s="74"/>
-    </row>
-    <row r="50" spans="1:39" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN49" s="74"/>
+      <c r="AO49" s="74"/>
+    </row>
+    <row r="50" spans="1:41" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>195</v>
       </c>
@@ -5485,8 +5625,10 @@
       <c r="AE50" s="8"/>
       <c r="AL50" s="74"/>
       <c r="AM50" s="74"/>
-    </row>
-    <row r="51" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN50" s="74"/>
+      <c r="AO50" s="74"/>
+    </row>
+    <row r="51" spans="1:41" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>195</v>
       </c>
@@ -5530,8 +5672,10 @@
       <c r="AE51" s="8"/>
       <c r="AL51" s="74"/>
       <c r="AM51" s="74"/>
-    </row>
-    <row r="52" spans="1:39" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN51" s="74"/>
+      <c r="AO51" s="74"/>
+    </row>
+    <row r="52" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="31" t="s">
         <v>195</v>
       </c>
@@ -5575,8 +5719,10 @@
       <c r="AE52" s="8"/>
       <c r="AL52" s="74"/>
       <c r="AM52" s="74"/>
-    </row>
-    <row r="53" spans="1:39" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN52" s="74"/>
+      <c r="AO52" s="74"/>
+    </row>
+    <row r="53" spans="1:41" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="31" t="s">
         <v>195</v>
       </c>
@@ -5620,8 +5766,10 @@
       <c r="AE53" s="8"/>
       <c r="AL53" s="74"/>
       <c r="AM53" s="74"/>
-    </row>
-    <row r="54" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN53" s="74"/>
+      <c r="AO53" s="74"/>
+    </row>
+    <row r="54" spans="1:41" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="31" t="s">
         <v>195</v>
       </c>
@@ -5665,8 +5813,10 @@
       <c r="AE54" s="8"/>
       <c r="AL54" s="74"/>
       <c r="AM54" s="74"/>
-    </row>
-    <row r="55" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN54" s="74"/>
+      <c r="AO54" s="74"/>
+    </row>
+    <row r="55" spans="1:41" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="31" t="s">
         <v>195</v>
       </c>
@@ -5710,8 +5860,10 @@
       <c r="AE55" s="8"/>
       <c r="AL55" s="74"/>
       <c r="AM55" s="74"/>
-    </row>
-    <row r="56" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN55" s="74"/>
+      <c r="AO55" s="74"/>
+    </row>
+    <row r="56" spans="1:41" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="31" t="s">
         <v>195</v>
       </c>
@@ -5755,8 +5907,10 @@
       <c r="AE56" s="8"/>
       <c r="AL56" s="74"/>
       <c r="AM56" s="74"/>
-    </row>
-    <row r="57" spans="1:39" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN56" s="74"/>
+      <c r="AO56" s="74"/>
+    </row>
+    <row r="57" spans="1:41" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="73" t="s">
         <v>195</v>
       </c>
@@ -5806,8 +5960,10 @@
       <c r="AE57" s="8"/>
       <c r="AL57" s="74"/>
       <c r="AM57" s="74"/>
-    </row>
-    <row r="58" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN57" s="74"/>
+      <c r="AO57" s="74"/>
+    </row>
+    <row r="58" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="29" t="s">
         <v>74</v>
       </c>
@@ -5895,8 +6051,10 @@
       <c r="AE58" s="8"/>
       <c r="AL58" s="74"/>
       <c r="AM58" s="74"/>
-    </row>
-    <row r="59" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN58" s="74"/>
+      <c r="AO58" s="74"/>
+    </row>
+    <row r="59" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="11" t="s">
         <v>54</v>
       </c>
@@ -5947,7 +6105,7 @@
       <c r="AD59" s="20"/>
       <c r="AE59" s="8"/>
     </row>
-    <row r="60" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="69" t="s">
         <v>54</v>
       </c>
@@ -6039,8 +6197,10 @@
       <c r="AE60" s="8"/>
       <c r="AL60" s="74"/>
       <c r="AM60" s="74"/>
-    </row>
-    <row r="61" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN60" s="74"/>
+      <c r="AO60" s="74"/>
+    </row>
+    <row r="61" spans="1:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="69" t="s">
         <v>54</v>
       </c>
@@ -6132,8 +6292,14 @@
       <c r="AE61" s="8"/>
       <c r="AL61" s="74"/>
       <c r="AM61" s="74"/>
-    </row>
-    <row r="62" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN61" s="74" t="s">
+        <v>515</v>
+      </c>
+      <c r="AO61" s="74">
+        <v>6862615185</v>
+      </c>
+    </row>
+    <row r="62" spans="1:41" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="80" t="s">
         <v>54</v>
       </c>
@@ -6225,8 +6391,14 @@
       <c r="AE62" s="8"/>
       <c r="AL62" s="74"/>
       <c r="AM62" s="74"/>
-    </row>
-    <row r="63" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN62" s="74" t="s">
+        <v>516</v>
+      </c>
+      <c r="AO62" s="74">
+        <v>68605616540</v>
+      </c>
+    </row>
+    <row r="63" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="69" t="s">
         <v>54</v>
       </c>
@@ -6318,8 +6490,14 @@
       <c r="AE63" s="8"/>
       <c r="AL63" s="74"/>
       <c r="AM63" s="74"/>
-    </row>
-    <row r="64" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN63" s="74" t="s">
+        <v>517</v>
+      </c>
+      <c r="AO63" s="74">
+        <v>6860546848</v>
+      </c>
+    </row>
+    <row r="64" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="69" t="s">
         <v>54</v>
       </c>
@@ -6411,8 +6589,14 @@
       <c r="AE64" s="8"/>
       <c r="AL64" s="74"/>
       <c r="AM64" s="74"/>
-    </row>
-    <row r="65" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN64" s="74" t="s">
+        <v>518</v>
+      </c>
+      <c r="AO64" s="74">
+        <v>6863214984</v>
+      </c>
+    </row>
+    <row r="65" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="69" t="s">
         <v>54</v>
       </c>
@@ -6504,8 +6688,14 @@
       <c r="AE65" s="8"/>
       <c r="AL65" s="74"/>
       <c r="AM65" s="74"/>
-    </row>
-    <row r="66" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN65" s="74" t="s">
+        <v>519</v>
+      </c>
+      <c r="AO65" s="74">
+        <v>68664524655</v>
+      </c>
+    </row>
+    <row r="66" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="83" t="s">
         <v>104</v>
       </c>
@@ -6585,8 +6775,14 @@
       <c r="AE66" s="8"/>
       <c r="AL66" s="74"/>
       <c r="AM66" s="74"/>
-    </row>
-    <row r="67" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN66" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="AO66" s="74">
+        <v>686684198426</v>
+      </c>
+    </row>
+    <row r="67" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="69" t="s">
         <v>54</v>
       </c>
@@ -6678,8 +6874,14 @@
       <c r="AE67" s="8"/>
       <c r="AL67" s="74"/>
       <c r="AM67" s="74"/>
-    </row>
-    <row r="68" spans="1:39" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN67" s="74" t="s">
+        <v>521</v>
+      </c>
+      <c r="AO67" s="74">
+        <v>686698798142</v>
+      </c>
+    </row>
+    <row r="68" spans="1:41" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="69" t="s">
         <v>54</v>
       </c>
@@ -6771,8 +6973,14 @@
       <c r="AE68" s="8"/>
       <c r="AL68" s="123"/>
       <c r="AM68" s="123"/>
-    </row>
-    <row r="69" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN68" s="123" t="s">
+        <v>522</v>
+      </c>
+      <c r="AO68" s="123">
+        <v>6864982465</v>
+      </c>
+    </row>
+    <row r="69" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="69" t="s">
         <v>54</v>
       </c>
@@ -6864,8 +7072,14 @@
       <c r="AE69" s="8"/>
       <c r="AL69" s="74"/>
       <c r="AM69" s="74"/>
-    </row>
-    <row r="70" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN69" s="74" t="s">
+        <v>523</v>
+      </c>
+      <c r="AO69" s="74">
+        <v>6866874182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="69" t="s">
         <v>54</v>
       </c>
@@ -6957,8 +7171,14 @@
       <c r="AE70" s="8"/>
       <c r="AL70" s="74"/>
       <c r="AM70" s="74"/>
-    </row>
-    <row r="71" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN70" s="74" t="s">
+        <v>524</v>
+      </c>
+      <c r="AO70" s="74">
+        <v>68654198765</v>
+      </c>
+    </row>
+    <row r="71" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="69" t="s">
         <v>54</v>
       </c>
@@ -7050,8 +7270,14 @@
       <c r="AE71" s="8"/>
       <c r="AL71" s="74"/>
       <c r="AM71" s="74"/>
-    </row>
-    <row r="72" spans="1:39" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN71" s="74" t="s">
+        <v>525</v>
+      </c>
+      <c r="AO71" s="74">
+        <v>686491871654</v>
+      </c>
+    </row>
+    <row r="72" spans="1:41" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="69" t="s">
         <v>54</v>
       </c>
@@ -7143,8 +7369,10 @@
       <c r="AE72" s="8"/>
       <c r="AL72" s="74"/>
       <c r="AM72" s="74"/>
-    </row>
-    <row r="73" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN72" s="74"/>
+      <c r="AO72" s="74"/>
+    </row>
+    <row r="73" spans="1:41" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="69" t="s">
         <v>54</v>
       </c>
@@ -7236,8 +7464,10 @@
       <c r="AE73" s="8"/>
       <c r="AL73" s="74"/>
       <c r="AM73" s="74"/>
-    </row>
-    <row r="74" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN73" s="74"/>
+      <c r="AO73" s="74"/>
+    </row>
+    <row r="74" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="69" t="s">
         <v>54</v>
       </c>
@@ -7329,8 +7559,10 @@
       <c r="AE74" s="8"/>
       <c r="AL74" s="74"/>
       <c r="AM74" s="74"/>
-    </row>
-    <row r="75" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN74" s="74"/>
+      <c r="AO74" s="74"/>
+    </row>
+    <row r="75" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="69" t="s">
         <v>54</v>
       </c>
@@ -7422,8 +7654,10 @@
       <c r="AE75" s="8"/>
       <c r="AL75" s="74"/>
       <c r="AM75" s="74"/>
-    </row>
-    <row r="76" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN75" s="74"/>
+      <c r="AO75" s="74"/>
+    </row>
+    <row r="76" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="69" t="s">
         <v>54</v>
       </c>
@@ -7515,8 +7749,10 @@
       <c r="AE76" s="8"/>
       <c r="AL76" s="74"/>
       <c r="AM76" s="74"/>
-    </row>
-    <row r="77" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN76" s="74"/>
+      <c r="AO76" s="74"/>
+    </row>
+    <row r="77" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="69" t="s">
         <v>54</v>
       </c>
@@ -7608,8 +7844,10 @@
       <c r="AE77" s="8"/>
       <c r="AL77" s="74"/>
       <c r="AM77" s="74"/>
-    </row>
-    <row r="78" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN77" s="74"/>
+      <c r="AO77" s="74"/>
+    </row>
+    <row r="78" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="69" t="s">
         <v>54</v>
       </c>
@@ -7691,8 +7929,10 @@
       <c r="AE78" s="8"/>
       <c r="AL78" s="74"/>
       <c r="AM78" s="74"/>
-    </row>
-    <row r="79" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN78" s="74"/>
+      <c r="AO78" s="74"/>
+    </row>
+    <row r="79" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="69" t="s">
         <v>54</v>
       </c>
@@ -7782,8 +8022,10 @@
       <c r="AE79" s="9"/>
       <c r="AL79" s="74"/>
       <c r="AM79" s="74"/>
-    </row>
-    <row r="80" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN79" s="74"/>
+      <c r="AO79" s="74"/>
+    </row>
+    <row r="80" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="31" t="s">
         <v>104</v>
       </c>
@@ -7827,8 +8069,10 @@
       <c r="AE80" s="8"/>
       <c r="AL80" s="74"/>
       <c r="AM80" s="74"/>
-    </row>
-    <row r="81" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN80" s="74"/>
+      <c r="AO80" s="74"/>
+    </row>
+    <row r="81" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="31" t="s">
         <v>104</v>
       </c>
@@ -7872,8 +8116,10 @@
       <c r="AE81" s="8"/>
       <c r="AL81" s="74"/>
       <c r="AM81" s="74"/>
-    </row>
-    <row r="82" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN81" s="74"/>
+      <c r="AO81" s="74"/>
+    </row>
+    <row r="82" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="31" t="s">
         <v>104</v>
       </c>
@@ -7917,8 +8163,10 @@
       <c r="AE82" s="8"/>
       <c r="AL82" s="74"/>
       <c r="AM82" s="74"/>
-    </row>
-    <row r="83" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN82" s="74"/>
+      <c r="AO82" s="74"/>
+    </row>
+    <row r="83" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="31" t="s">
         <v>104</v>
       </c>
@@ -7962,8 +8210,10 @@
       <c r="AE83" s="8"/>
       <c r="AL83" s="74"/>
       <c r="AM83" s="74"/>
-    </row>
-    <row r="84" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN83" s="74"/>
+      <c r="AO83" s="74"/>
+    </row>
+    <row r="84" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="31" t="s">
         <v>104</v>
       </c>
@@ -8007,8 +8257,10 @@
       <c r="AE84" s="8"/>
       <c r="AL84" s="74"/>
       <c r="AM84" s="74"/>
-    </row>
-    <row r="85" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN84" s="74"/>
+      <c r="AO84" s="74"/>
+    </row>
+    <row r="85" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="29" t="s">
         <v>74</v>
       </c>
@@ -8064,8 +8316,10 @@
       <c r="AE85" s="8"/>
       <c r="AL85" s="74"/>
       <c r="AM85" s="74"/>
-    </row>
-    <row r="86" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN85" s="74"/>
+      <c r="AO85" s="74"/>
+    </row>
+    <row r="86" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="31" t="s">
         <v>104</v>
       </c>
@@ -8109,8 +8363,10 @@
       <c r="AE86" s="8"/>
       <c r="AL86" s="74"/>
       <c r="AM86" s="74"/>
-    </row>
-    <row r="87" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN86" s="74"/>
+      <c r="AO86" s="74"/>
+    </row>
+    <row r="87" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="29" t="s">
         <v>74</v>
       </c>
@@ -8164,8 +8420,10 @@
       <c r="AE87" s="7"/>
       <c r="AL87" s="74"/>
       <c r="AM87" s="74"/>
-    </row>
-    <row r="88" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN87" s="74"/>
+      <c r="AO87" s="74"/>
+    </row>
+    <row r="88" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="31" t="s">
         <v>195</v>
       </c>
@@ -8209,8 +8467,10 @@
       <c r="AE88" s="7"/>
       <c r="AL88" s="74"/>
       <c r="AM88" s="74"/>
-    </row>
-    <row r="89" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN88" s="74"/>
+      <c r="AO88" s="74"/>
+    </row>
+    <row r="89" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="31" t="s">
         <v>195</v>
       </c>
@@ -8254,8 +8514,10 @@
       <c r="AE89" s="7"/>
       <c r="AL89" s="74"/>
       <c r="AM89" s="74"/>
-    </row>
-    <row r="90" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN89" s="74"/>
+      <c r="AO89" s="74"/>
+    </row>
+    <row r="90" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="29" t="s">
         <v>74</v>
       </c>
@@ -8303,8 +8565,10 @@
       <c r="AE90" s="7"/>
       <c r="AL90" s="74"/>
       <c r="AM90" s="74"/>
-    </row>
-    <row r="91" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN90" s="74"/>
+      <c r="AO90" s="74"/>
+    </row>
+    <row r="91" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="69" t="s">
         <v>54</v>
       </c>
@@ -8396,8 +8660,10 @@
       <c r="AE91" s="7"/>
       <c r="AL91" s="74"/>
       <c r="AM91" s="74"/>
-    </row>
-    <row r="92" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN91" s="74"/>
+      <c r="AO91" s="74"/>
+    </row>
+    <row r="92" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="69" t="s">
         <v>54</v>
       </c>
@@ -8489,8 +8755,10 @@
       <c r="AE92" s="7"/>
       <c r="AL92" s="74"/>
       <c r="AM92" s="74"/>
-    </row>
-    <row r="93" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN92" s="74"/>
+      <c r="AO92" s="74"/>
+    </row>
+    <row r="93" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="69" t="s">
         <v>54</v>
       </c>
@@ -8582,8 +8850,10 @@
       <c r="AE93" s="7"/>
       <c r="AL93" s="74"/>
       <c r="AM93" s="74"/>
-    </row>
-    <row r="94" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN93" s="74"/>
+      <c r="AO93" s="74"/>
+    </row>
+    <row r="94" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="69" t="s">
         <v>54</v>
       </c>
@@ -8631,8 +8901,10 @@
       <c r="AE94" s="7"/>
       <c r="AL94" s="74"/>
       <c r="AM94" s="74"/>
-    </row>
-    <row r="95" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN94" s="74"/>
+      <c r="AO94" s="74"/>
+    </row>
+    <row r="95" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="31" t="s">
         <v>104</v>
       </c>
@@ -8676,8 +8948,10 @@
       <c r="AE95" s="7"/>
       <c r="AL95" s="74"/>
       <c r="AM95" s="74"/>
-    </row>
-    <row r="96" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN95" s="74"/>
+      <c r="AO95" s="74"/>
+    </row>
+    <row r="96" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
         <v>104</v>
       </c>
@@ -8721,8 +8995,10 @@
       <c r="AE96" s="7"/>
       <c r="AL96" s="74"/>
       <c r="AM96" s="74"/>
-    </row>
-    <row r="97" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN96" s="74"/>
+      <c r="AO96" s="74"/>
+    </row>
+    <row r="97" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="31" t="s">
         <v>104</v>
       </c>
@@ -8766,8 +9042,10 @@
       <c r="AE97" s="7"/>
       <c r="AL97" s="74"/>
       <c r="AM97" s="74"/>
-    </row>
-    <row r="98" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN97" s="74"/>
+      <c r="AO97" s="74"/>
+    </row>
+    <row r="98" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="31" t="s">
         <v>104</v>
       </c>
@@ -8811,8 +9089,10 @@
       <c r="AE98" s="7"/>
       <c r="AL98" s="74"/>
       <c r="AM98" s="74"/>
-    </row>
-    <row r="99" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN98" s="74"/>
+      <c r="AO98" s="74"/>
+    </row>
+    <row r="99" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="31" t="s">
         <v>104</v>
       </c>
@@ -8856,8 +9136,10 @@
       <c r="AE99" s="7"/>
       <c r="AL99" s="74"/>
       <c r="AM99" s="74"/>
-    </row>
-    <row r="100" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN99" s="74"/>
+      <c r="AO99" s="74"/>
+    </row>
+    <row r="100" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="31" t="s">
         <v>104</v>
       </c>
@@ -8901,8 +9183,10 @@
       <c r="AE100" s="7"/>
       <c r="AL100" s="74"/>
       <c r="AM100" s="74"/>
-    </row>
-    <row r="101" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN100" s="74"/>
+      <c r="AO100" s="74"/>
+    </row>
+    <row r="101" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="31" t="s">
         <v>104</v>
       </c>
@@ -8946,8 +9230,10 @@
       <c r="AE101" s="7"/>
       <c r="AL101" s="74"/>
       <c r="AM101" s="74"/>
-    </row>
-    <row r="102" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN101" s="74"/>
+      <c r="AO101" s="74"/>
+    </row>
+    <row r="102" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="31" t="s">
         <v>104</v>
       </c>
@@ -8991,8 +9277,10 @@
       <c r="AE102" s="7"/>
       <c r="AL102" s="74"/>
       <c r="AM102" s="74"/>
-    </row>
-    <row r="103" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN102" s="74"/>
+      <c r="AO102" s="74"/>
+    </row>
+    <row r="103" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="31" t="s">
         <v>104</v>
       </c>
@@ -9036,8 +9324,10 @@
       <c r="AE103" s="7"/>
       <c r="AL103" s="74"/>
       <c r="AM103" s="74"/>
-    </row>
-    <row r="104" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN103" s="74"/>
+      <c r="AO103" s="74"/>
+    </row>
+    <row r="104" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="31" t="s">
         <v>104</v>
       </c>
@@ -9081,8 +9371,10 @@
       <c r="AE104" s="7"/>
       <c r="AL104" s="74"/>
       <c r="AM104" s="74"/>
-    </row>
-    <row r="105" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN104" s="74"/>
+      <c r="AO104" s="74"/>
+    </row>
+    <row r="105" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="31" t="s">
         <v>104</v>
       </c>
@@ -9126,8 +9418,10 @@
       <c r="AE105" s="7"/>
       <c r="AL105" s="74"/>
       <c r="AM105" s="74"/>
-    </row>
-    <row r="106" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN105" s="74"/>
+      <c r="AO105" s="74"/>
+    </row>
+    <row r="106" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="31" t="s">
         <v>104</v>
       </c>
@@ -9171,8 +9465,10 @@
       <c r="AE106" s="7"/>
       <c r="AL106" s="74"/>
       <c r="AM106" s="74"/>
-    </row>
-    <row r="107" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN106" s="74"/>
+      <c r="AO106" s="74"/>
+    </row>
+    <row r="107" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="31" t="s">
         <v>104</v>
       </c>
@@ -9216,8 +9512,10 @@
       <c r="AE107" s="7"/>
       <c r="AL107" s="74"/>
       <c r="AM107" s="74"/>
-    </row>
-    <row r="108" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN107" s="74"/>
+      <c r="AO107" s="74"/>
+    </row>
+    <row r="108" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="31" t="s">
         <v>104</v>
       </c>
@@ -9261,8 +9559,10 @@
       <c r="AE108" s="7"/>
       <c r="AL108" s="74"/>
       <c r="AM108" s="74"/>
-    </row>
-    <row r="109" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN108" s="74"/>
+      <c r="AO108" s="74"/>
+    </row>
+    <row r="109" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="31" t="s">
         <v>104</v>
       </c>
@@ -9306,8 +9606,10 @@
       <c r="AE109" s="7"/>
       <c r="AL109" s="74"/>
       <c r="AM109" s="74"/>
-    </row>
-    <row r="110" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN109" s="74"/>
+      <c r="AO109" s="74"/>
+    </row>
+    <row r="110" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="31" t="s">
         <v>104</v>
       </c>
@@ -9351,8 +9653,10 @@
       <c r="AE110" s="7"/>
       <c r="AL110" s="74"/>
       <c r="AM110" s="74"/>
-    </row>
-    <row r="111" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN110" s="74"/>
+      <c r="AO110" s="74"/>
+    </row>
+    <row r="111" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="31" t="s">
         <v>104</v>
       </c>
@@ -9396,8 +9700,10 @@
       <c r="AE111" s="7"/>
       <c r="AL111" s="74"/>
       <c r="AM111" s="74"/>
-    </row>
-    <row r="112" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN111" s="74"/>
+      <c r="AO111" s="74"/>
+    </row>
+    <row r="112" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="31" t="s">
         <v>104</v>
       </c>
@@ -9441,8 +9747,10 @@
       <c r="AE112" s="7"/>
       <c r="AL112" s="74"/>
       <c r="AM112" s="74"/>
-    </row>
-    <row r="113" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN112" s="74"/>
+      <c r="AO112" s="74"/>
+    </row>
+    <row r="113" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="31" t="s">
         <v>104</v>
       </c>
@@ -9486,8 +9794,10 @@
       <c r="AE113" s="7"/>
       <c r="AL113" s="74"/>
       <c r="AM113" s="74"/>
-    </row>
-    <row r="114" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN113" s="74"/>
+      <c r="AO113" s="74"/>
+    </row>
+    <row r="114" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="31" t="s">
         <v>104</v>
       </c>
@@ -9531,8 +9841,10 @@
       <c r="AE114" s="7"/>
       <c r="AL114" s="74"/>
       <c r="AM114" s="74"/>
-    </row>
-    <row r="115" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN114" s="74"/>
+      <c r="AO114" s="74"/>
+    </row>
+    <row r="115" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="31" t="s">
         <v>104</v>
       </c>
@@ -9576,8 +9888,10 @@
       <c r="AE115" s="7"/>
       <c r="AL115" s="74"/>
       <c r="AM115" s="74"/>
-    </row>
-    <row r="116" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN115" s="74"/>
+      <c r="AO115" s="74"/>
+    </row>
+    <row r="116" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="31" t="s">
         <v>104</v>
       </c>
@@ -9621,8 +9935,10 @@
       <c r="AE116" s="7"/>
       <c r="AL116" s="74"/>
       <c r="AM116" s="74"/>
-    </row>
-    <row r="117" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN116" s="74"/>
+      <c r="AO116" s="74"/>
+    </row>
+    <row r="117" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="31" t="s">
         <v>104</v>
       </c>
@@ -9666,8 +9982,10 @@
       <c r="AE117" s="7"/>
       <c r="AL117" s="74"/>
       <c r="AM117" s="74"/>
-    </row>
-    <row r="118" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN117" s="74"/>
+      <c r="AO117" s="74"/>
+    </row>
+    <row r="118" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="31" t="s">
         <v>104</v>
       </c>
@@ -9711,8 +10029,10 @@
       <c r="AE118" s="7"/>
       <c r="AL118" s="74"/>
       <c r="AM118" s="74"/>
-    </row>
-    <row r="119" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN118" s="74"/>
+      <c r="AO118" s="74"/>
+    </row>
+    <row r="119" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="31" t="s">
         <v>104</v>
       </c>
@@ -9756,8 +10076,10 @@
       <c r="AE119" s="7"/>
       <c r="AL119" s="74"/>
       <c r="AM119" s="74"/>
-    </row>
-    <row r="120" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN119" s="74"/>
+      <c r="AO119" s="74"/>
+    </row>
+    <row r="120" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="31" t="s">
         <v>104</v>
       </c>
@@ -9801,8 +10123,10 @@
       <c r="AE120" s="7"/>
       <c r="AL120" s="74"/>
       <c r="AM120" s="74"/>
-    </row>
-    <row r="121" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN120" s="74"/>
+      <c r="AO120" s="74"/>
+    </row>
+    <row r="121" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="31" t="s">
         <v>104</v>
       </c>
@@ -9846,8 +10170,10 @@
       <c r="AE121" s="7"/>
       <c r="AL121" s="74"/>
       <c r="AM121" s="74"/>
-    </row>
-    <row r="122" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN121" s="74"/>
+      <c r="AO121" s="74"/>
+    </row>
+    <row r="122" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="31" t="s">
         <v>104</v>
       </c>
@@ -9891,8 +10217,10 @@
       <c r="AE122" s="7"/>
       <c r="AL122" s="74"/>
       <c r="AM122" s="74"/>
-    </row>
-    <row r="123" spans="1:39" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN122" s="74"/>
+      <c r="AO122" s="74"/>
+    </row>
+    <row r="123" spans="1:41" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="31" t="s">
         <v>104</v>
       </c>
@@ -9936,8 +10264,10 @@
       <c r="AE123" s="7"/>
       <c r="AL123" s="124"/>
       <c r="AM123" s="124"/>
-    </row>
-    <row r="124" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN123" s="124"/>
+      <c r="AO123" s="124"/>
+    </row>
+    <row r="124" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="31" t="s">
         <v>104</v>
       </c>
@@ -9981,8 +10311,10 @@
       <c r="AE124" s="7"/>
       <c r="AL124" s="74"/>
       <c r="AM124" s="74"/>
-    </row>
-    <row r="125" spans="1:39" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN124" s="74"/>
+      <c r="AO124" s="74"/>
+    </row>
+    <row r="125" spans="1:41" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="31" t="s">
         <v>104</v>
       </c>
@@ -10026,8 +10358,10 @@
       <c r="AE125" s="7"/>
       <c r="AL125" s="124"/>
       <c r="AM125" s="124"/>
-    </row>
-    <row r="126" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN125" s="124"/>
+      <c r="AO125" s="124"/>
+    </row>
+    <row r="126" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="31" t="s">
         <v>104</v>
       </c>
@@ -10071,8 +10405,10 @@
       <c r="AE126" s="7"/>
       <c r="AL126" s="74"/>
       <c r="AM126" s="74"/>
-    </row>
-    <row r="127" spans="1:39" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN126" s="74"/>
+      <c r="AO126" s="74"/>
+    </row>
+    <row r="127" spans="1:41" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="31" t="s">
         <v>104</v>
       </c>
@@ -10116,8 +10452,10 @@
       <c r="AE127" s="7"/>
       <c r="AL127" s="124"/>
       <c r="AM127" s="124"/>
-    </row>
-    <row r="128" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN127" s="124"/>
+      <c r="AO127" s="124"/>
+    </row>
+    <row r="128" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="31" t="s">
         <v>104</v>
       </c>
@@ -10161,8 +10499,10 @@
       <c r="AE128" s="7"/>
       <c r="AL128" s="74"/>
       <c r="AM128" s="74"/>
-    </row>
-    <row r="129" spans="1:39" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN128" s="74"/>
+      <c r="AO128" s="74"/>
+    </row>
+    <row r="129" spans="1:41" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="31" t="s">
         <v>104</v>
       </c>
@@ -10206,8 +10546,10 @@
       <c r="AE129" s="7"/>
       <c r="AL129" s="124"/>
       <c r="AM129" s="124"/>
-    </row>
-    <row r="130" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN129" s="124"/>
+      <c r="AO129" s="124"/>
+    </row>
+    <row r="130" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="31" t="s">
         <v>104</v>
       </c>
@@ -10251,8 +10593,10 @@
       <c r="AE130" s="7"/>
       <c r="AL130" s="74"/>
       <c r="AM130" s="74"/>
-    </row>
-    <row r="131" spans="1:39" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN130" s="74"/>
+      <c r="AO130" s="74"/>
+    </row>
+    <row r="131" spans="1:41" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="31" t="s">
         <v>104</v>
       </c>
@@ -10296,8 +10640,10 @@
       <c r="AE131" s="7"/>
       <c r="AL131" s="124"/>
       <c r="AM131" s="124"/>
-    </row>
-    <row r="132" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN131" s="124"/>
+      <c r="AO131" s="124"/>
+    </row>
+    <row r="132" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="31" t="s">
         <v>104</v>
       </c>
@@ -10341,8 +10687,10 @@
       <c r="AE132" s="7"/>
       <c r="AL132" s="74"/>
       <c r="AM132" s="74"/>
-    </row>
-    <row r="133" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN132" s="74"/>
+      <c r="AO132" s="74"/>
+    </row>
+    <row r="133" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="31" t="s">
         <v>104</v>
       </c>
@@ -10386,8 +10734,10 @@
       <c r="AE133" s="7"/>
       <c r="AL133" s="74"/>
       <c r="AM133" s="74"/>
-    </row>
-    <row r="134" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN133" s="74"/>
+      <c r="AO133" s="74"/>
+    </row>
+    <row r="134" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="31" t="s">
         <v>104</v>
       </c>
@@ -10431,8 +10781,10 @@
       <c r="AE134" s="7"/>
       <c r="AL134" s="74"/>
       <c r="AM134" s="74"/>
-    </row>
-    <row r="135" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN134" s="74"/>
+      <c r="AO134" s="74"/>
+    </row>
+    <row r="135" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="31" t="s">
         <v>104</v>
       </c>
@@ -10476,8 +10828,10 @@
       <c r="AE135" s="7"/>
       <c r="AL135" s="74"/>
       <c r="AM135" s="74"/>
-    </row>
-    <row r="136" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN135" s="74"/>
+      <c r="AO135" s="74"/>
+    </row>
+    <row r="136" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="31" t="s">
         <v>104</v>
       </c>
@@ -10521,8 +10875,10 @@
       <c r="AE136" s="7"/>
       <c r="AL136" s="74"/>
       <c r="AM136" s="74"/>
-    </row>
-    <row r="137" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN136" s="74"/>
+      <c r="AO136" s="74"/>
+    </row>
+    <row r="137" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="31" t="s">
         <v>104</v>
       </c>
@@ -10566,8 +10922,10 @@
       <c r="AE137" s="7"/>
       <c r="AL137" s="74"/>
       <c r="AM137" s="74"/>
-    </row>
-    <row r="138" spans="1:39" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AN137" s="74"/>
+      <c r="AO137" s="74"/>
+    </row>
+    <row r="138" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="31" t="s">
         <v>104</v>
       </c>
@@ -10611,8 +10969,10 @@
       <c r="AE138" s="7"/>
       <c r="AL138" s="74"/>
       <c r="AM138" s="74"/>
-    </row>
-    <row r="139" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AN138" s="74"/>
+      <c r="AO138" s="74"/>
+    </row>
+    <row r="139" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="74"/>
       <c r="B139" s="74"/>
       <c r="C139" s="74"/>
@@ -10646,6 +11006,8 @@
       <c r="AE139" s="6"/>
       <c r="AL139" s="74"/>
       <c r="AM139" s="74"/>
+      <c r="AN139" s="74"/>
+      <c r="AO139" s="74"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AF138" xr:uid="{00000000-0001-0000-0300-000000000000}">
@@ -10679,7 +11041,7 @@
   <customSheetViews>
     <customSheetView guid="{0B1C18F8-03D6-48D4-A50B-BF1EDFC553E5}" filter="1" showAutoFilter="1">
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-      <autoFilter ref="C2:D138" xr:uid="{5A7F161B-6F6D-4928-8987-0D283175BB0A}"/>
+      <autoFilter ref="C2:D138" xr:uid="{15C8C2E0-66B9-40D5-A7AE-094355D37EF3}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="2">
